--- a/イベント一覧.xlsx
+++ b/イベント一覧.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayur\OneDrive\デスクトップ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22486D3A-9BD4-48C3-84F2-28D793704EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A2D809-B71A-474D-89CF-4E77FBDF6361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="7" xr2:uid="{3435D29D-17A9-4A87-B931-BE3421F071AC}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" activeTab="8" xr2:uid="{3435D29D-17A9-4A87-B931-BE3421F071AC}"/>
   </bookViews>
   <sheets>
     <sheet name="氷原支配者" sheetId="1" r:id="rId1"/>
-    <sheet name="童心の宴" sheetId="2" r:id="rId2"/>
+    <sheet name="同盟大作戦" sheetId="4" r:id="rId2"/>
     <sheet name="SVS準備" sheetId="3" r:id="rId3"/>
-    <sheet name="同盟大作戦" sheetId="4" r:id="rId4"/>
-    <sheet name="軍備競技(月火)" sheetId="7" r:id="rId5"/>
-    <sheet name="軍備競技(金土)" sheetId="8" r:id="rId6"/>
-    <sheet name="士官計画(水木)" sheetId="5" r:id="rId7"/>
-    <sheet name="士官計画(日月)" sheetId="6" r:id="rId8"/>
+    <sheet name="軍備競技(月火)" sheetId="7" r:id="rId4"/>
+    <sheet name="軍備競技(金土)" sheetId="8" r:id="rId5"/>
+    <sheet name="士官計画(水木)" sheetId="5" r:id="rId6"/>
+    <sheet name="士官計画(日月)" sheetId="6" r:id="rId7"/>
+    <sheet name="童心の宴" sheetId="2" r:id="rId8"/>
+    <sheet name="野獣駆逐" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="25">
   <si>
     <t>項目名</t>
     <rPh sb="0" eb="3">
@@ -189,13 +190,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>獣</t>
-    <rPh sb="0" eb="1">
-      <t>ケモノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ダイヤ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -210,6 +204,13 @@
     <t>行商</t>
     <rPh sb="0" eb="2">
       <t>ギョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>野獣</t>
+    <rPh sb="0" eb="2">
+      <t>ヤジュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -773,22 +774,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -798,11 +799,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A04963C-33E9-455A-97C2-3CC59A7E5AF6}">
-  <dimension ref="A1:H17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B5B6C9-4E26-44CB-AD62-86B2C3CB91E2}">
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -824,136 +825,229 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
       <c r="G2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
         <v>15</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
       </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>19</v>
       </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
       <c r="E9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>13</v>
       </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
       <c r="F10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="G12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>20</v>
       </c>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
-        <v>24</v>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1115,7 +1209,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -1123,12 +1217,12 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -1139,7 +1233,7 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1149,11 +1243,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B5B6C9-4E26-44CB-AD62-86B2C3CB91E2}">
-  <dimension ref="A1:G17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0B39B41-C64C-43F8-8761-3503EB624C86}">
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1163,20 +1257,8 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1186,14 +1268,8 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1203,28 +1279,13 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1234,14 +1295,8 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1251,153 +1306,60 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
         <v>23</v>
-      </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1407,7 +1369,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0B39B41-C64C-43F8-8761-3503EB624C86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F5020F6-1C99-44D3-ABE4-7FC997E7BA96}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
@@ -1429,9 +1391,6 @@
       <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
@@ -1440,9 +1399,6 @@
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
@@ -1456,20 +1412,11 @@
       <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
@@ -1490,11 +1437,17 @@
       <c r="A10" t="s">
         <v>13</v>
       </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>18</v>
       </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
@@ -1508,22 +1461,22 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1533,7 +1486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F5020F6-1C99-44D3-ABE4-7FC997E7BA96}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53F1F949-F95D-4640-8597-06E8CC0F2C5F}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
@@ -1552,30 +1505,27 @@
       <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>11</v>
       </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
@@ -1596,6 +1546,12 @@
       <c r="A9" t="s">
         <v>19</v>
       </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
@@ -1604,6 +1560,9 @@
       <c r="B10" t="s">
         <v>15</v>
       </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
@@ -1612,6 +1571,9 @@
       <c r="B11" t="s">
         <v>15</v>
       </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
@@ -1625,22 +1587,22 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1650,7 +1612,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53F1F949-F95D-4640-8597-06E8CC0F2C5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B89C63-D6F3-4897-AF23-0D6977069742}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
@@ -1674,17 +1636,17 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
@@ -1695,6 +1657,12 @@
       <c r="A6" t="s">
         <v>10</v>
       </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
@@ -1710,12 +1678,6 @@
       <c r="A9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
@@ -1751,22 +1713,22 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1776,7 +1738,172 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B89C63-D6F3-4897-AF23-0D6977069742}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A04963C-33E9-455A-97C2-3CC59A7E5AF6}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{947F4C09-0C21-4FE7-B38F-50D43597EF86}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
@@ -1800,12 +1927,6 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
@@ -1821,12 +1942,6 @@
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
@@ -1847,23 +1962,11 @@
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
@@ -1877,22 +1980,28 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/イベント一覧.xlsx
+++ b/イベント一覧.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayur\OneDrive\デスクトップ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayur\OneDrive\デスクトップ\めも\my_app\260510 manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A2D809-B71A-474D-89CF-4E77FBDF6361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49113CC2-20F4-4504-A3A2-53F3A49FF294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" activeTab="8" xr2:uid="{3435D29D-17A9-4A87-B931-BE3421F071AC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" firstSheet="3" activeTab="9" xr2:uid="{3435D29D-17A9-4A87-B931-BE3421F071AC}"/>
   </bookViews>
   <sheets>
     <sheet name="氷原支配者" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="士官計画(日月)" sheetId="6" r:id="rId7"/>
     <sheet name="童心の宴" sheetId="2" r:id="rId8"/>
     <sheet name="野獣駆逐" sheetId="9" r:id="rId9"/>
+    <sheet name="サッカー" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="25">
   <si>
     <t>項目名</t>
     <rPh sb="0" eb="3">
@@ -798,6 +799,165 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85504DFA-34F2-43C2-A97D-AF3D812E3646}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B5B6C9-4E26-44CB-AD62-86B2C3CB91E2}">
   <dimension ref="A1:G17"/>
